--- a/nursing/フォーマット/04_相談支援様式/04_アセスメントシート（相談支援版）.xlsx
+++ b/nursing/フォーマット/04_相談支援様式/04_アセスメントシート（相談支援版）.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="アセスメント票（相談支援）" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="アセスメント(相談)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,31 +26,37 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <color rgb="FF0E7490"/>
-      <sz val="13"/>
+      <color rgb="00163A2B"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <sz val="9"/>
+      <color rgb="00163A2B"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <color rgb="00283129"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <i val="1"/>
-      <color rgb="FF6B7280"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -62,21 +68,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCFFAFE"/>
+        <fgColor rgb="00E4EFE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E7490"/>
+        <fgColor rgb="001F4D3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
+        <fgColor rgb="00F6EDDA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -85,38 +91,60 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <bottom style="medium">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DAD3C2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DAD3C2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DAD3C2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DAD3C2"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00A9854A"/>
+      </left>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,272 +508,343 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>アセスメントシート（相談支援・計画相談用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
+          <t>アセスメントシート（相談支援）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>実施日：　　年　月　日　実施者：　　　　　　　参加者：本人 / 家族（　　）/ キーパーソン（　　）/ その他（　　）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>利用者氏名</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>（様）</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>生年月日</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　年　月　日（　歳）</t>
-        </is>
-      </c>
-    </row>
+          <t>本人の状況・環境・意向を多面的に把握し、サービス等利用計画の土台とする</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>障害の種別・等級</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>障害支援区分</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>区分　　　 / 認定日：</t>
-        </is>
-      </c>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>氏名 / 生年月日</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>住所・連絡先</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>〒</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>保護者・キーパーソン</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>実施日 / 実施者</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>主治医・医療機関</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>主傷病名</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>【本人の希望・将来の夢】</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>本人から直接聴取した希望（そのままの言葉で記録）：
-将来どんな生活をしたいか：</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>【現在の生活状況】</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>起床・就寝時刻、食事・服薬の自己管理、清潔管理、外出・移動の状況：
-居住形態：自宅（独居/家族と）/ グループホーム / その他</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>【障害・健康状態】</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>障害の状態（日常生活への影響、進行性の有無等）：
-服薬状況・通院状況：
-精神状態の波・体調悪化のサイン：</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>【就労・日中活動の状況】</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>現在の活動：
-就労能力・希望：
-経済状況（収入・工賃・年金等）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>【家族・社会関係】</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="50" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>同居家族・キーパーソンの状況：
-地域・コミュニティとの関係：</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>【現在利用中のサービス・支援】</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="50" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>サービス種別 / 事業所名 / 利用頻度：
-①
-②
-③</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>【相談に至った経緯・主訴】</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="50" customHeight="1">
-      <c r="A20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>【アセスメントから見えた課題・優先ニーズ】</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="70" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>優先課題①：
-優先課題②：
-優先課題③：</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">アセスメント実施者署名：　　　　　　　　　日付：　　年　月　日　確認者（管理者）：　　　　　　　　</t>
-        </is>
-      </c>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>障害種別 / 支援区分</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>情報源</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>□本人　□家族　□関係機関</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="8" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>1. 生活歴・現在の暮らし（住まい・日中活動）</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>2. 健康・医療（疾患・服薬・通院）</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>3. 日常生活動作（ADL/IADL）</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>4. コミュニケーション・対人・社会参加</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>5. 家族・インフォーマルな支え・経済</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>6. 本人の希望する生活・強み・課題整理</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>※ ICF（生活機能）の視点で「心身機能・活動・参加・環境因子・個人因子」を整理。本人中心で。</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="11" t="n"/>
+      <c r="G27" s="11" t="n"/>
+      <c r="H27" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="17">
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A9:H9"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="C6:H6"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A18:H18"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="C5:H5"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A6:B6"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>